--- a/卡牌清单.xlsx
+++ b/卡牌清单.xlsx
@@ -7,11 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="全部卡牌" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="卡牌清单" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="统计" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'全部卡牌'!$A$1:$M$111</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'卡牌清单'!$A$1:$O$109</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,11 +29,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -42,16 +57,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F4E3D"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E78"/>
+        <fgColor rgb="002B1F10"/>
+        <bgColor rgb="002B1F10"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -60,13 +71,17 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="00C0A886"/>
+      </left>
+      <right style="thin">
+        <color rgb="00C0A886"/>
+      </right>
+      <top style="thin">
+        <color rgb="00C0A886"/>
+      </top>
       <bottom style="thin">
-        <color rgb="00D9E2D0"/>
-      </bottom>
-    </border>
-    <border>
-      <bottom style="thin">
-        <color rgb="00D9E2F3"/>
+        <color rgb="00C0A886"/>
       </bottom>
     </border>
   </borders>
@@ -76,20 +91,14 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,88 +464,100 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M110"/>
+  <dimension ref="A1:O109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="56" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="56" customWidth="1" min="9" max="9"/>
-    <col width="28" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="34" customWidth="1" min="12" max="12"/>
-    <col width="48" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="6" customWidth="1" min="12" max="12"/>
+    <col width="4" customWidth="1" min="13" max="13"/>
+    <col width="45" customWidth="1" min="14" max="14"/>
+    <col width="35" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="4" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>名字</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>类型</t>
         </is>
       </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>战斗类型</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>稀有度</t>
         </is>
       </c>
-      <c r="F1" s="4" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>费用</t>
         </is>
       </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>功能</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>图片路径</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>中医说明</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>目标</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>效果ID</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>是否不可打出</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>九大体质初始卡牌</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>药方蓝图合成素材</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>副值</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>不可打出</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>消耗</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>幕</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TCM注</t>
         </is>
       </c>
     </row>
@@ -553,7 +574,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -563,39 +584,51 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>energy_max_heal</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>获得1点真气上限，并恢复3点生命。</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>/assets/cards_player/67.png</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>关元为保健要穴，温补下元。</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>energy_max_heal</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>阳虚质、特禀质</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -610,7 +643,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -623,32 +656,44 @@
           <t>普通</t>
         </is>
       </c>
-      <c r="F3" s="2" t="n">
-        <v>1</v>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>获得3点格挡。本回合每打出一张卡牌，获得1点格挡。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/40.png</t>
+          <t>block_per_card</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>艾叶辛苦温，温经止血，散寒止痛。</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>block_per_card</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
-      <c r="M3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>获得3点格挡。本回合每打出一张卡牌，获得1点格挡。</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>艾叶辛苦温，温经止血，散寒止痛。</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -663,7 +708,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -676,38 +721,46 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F4" s="2" t="n">
-        <v>0</v>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>使你在本场战斗中免疫下一次死亡，并恢复20%生命。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/angong.svg</t>
+          <t>revive_buff</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>干姜辛热，温中散寒，回阳通脉，温肺化饮。</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>revive_buff</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>阳虚质、特禀质</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>理中丸蓝图、小青龙汤蓝图</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>使你在本场战斗中免疫下一次死亡，并恢复20%生命。消耗。</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>干姜辛热，温中散寒，回阳通脉，温肺化饮。</t>
         </is>
       </c>
     </row>
@@ -724,7 +777,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -737,36 +790,40 @@
           <t>普通</t>
         </is>
       </c>
-      <c r="F5" s="2" t="n">
-        <v>1</v>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>yin_cleanse</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="inlineStr"/>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
           <t>移除自身1个负面状态。若有至少3层滋阴，改为移除所有负面状态。</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>/assets/cards_player/16.png</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>百合甘微寒，养阴润肺，清心安神。</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>yin_cleanse</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr"/>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -781,7 +838,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -794,38 +851,38 @@
           <t>普通</t>
         </is>
       </c>
-      <c r="F6" s="2" t="n">
-        <v>0</v>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
+          <t>单体</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>debuff_weak_draw</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
           <t>使一个敌人虚弱(造成的伤害减少25%)，抽1张牌。</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>/assets/cards_player/8.png</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>白芍苦酸微寒，养血调经，柔肝止痛。</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>debuff_weak_draw</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>平和质、气郁质</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>真武汤蓝图、小青龙汤蓝图</t>
         </is>
       </c>
     </row>
@@ -842,7 +899,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -852,41 +909,49 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>1</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>block_if_no_damage_strength</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
           <t>获得6点格挡。如果本回合未受到攻击伤害，获得2点力量。</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>/assets/cards_player/22.png</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>白术苦甘温，健脾益气，燥湿利水。</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>block_if_no_damage_strength</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr"/>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>气虚质、痰湿质</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>理中丸蓝图、四君子汤蓝图、真武汤蓝图</t>
         </is>
       </c>
     </row>
@@ -903,7 +968,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -916,36 +981,44 @@
           <t>普通</t>
         </is>
       </c>
-      <c r="F8" s="2" t="n">
-        <v>1</v>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>全体</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>aoe_debuff_heat</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>给予所有敌人1层热邪，抽1张牌。</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>/assets/cards_player/38.png</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>板蓝根苦寒，清热解毒，凉血利咽。</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>aoe_debuff_heat</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>湿热质</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -960,7 +1033,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -973,38 +1046,46 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F9" s="2" t="n">
-        <v>0</v>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>使所有敌人眩晕2回合。消耗。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/banxia.svg</t>
+          <t>aoe_stun</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>半夏辛温，燥湿化痰，降逆止呕，消痞散结。</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>aoe_stun</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>痰湿质</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>小柴胡汤蓝图、半夏厚朴汤蓝图、小青龙汤蓝图</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>使所有敌人眩晕2回合。消耗。</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>半夏辛温，燥湿化痰，降逆止呕，消痞散结。</t>
         </is>
       </c>
     </row>
@@ -1021,7 +1102,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1034,38 +1115,42 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F10" s="2" t="n">
-        <v>0</v>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>抽牌直到手牌达到5张。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/baohe.svg</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>桔梗苦辛平，宣肺利咽，祛痰排脓。</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
           <t>draw_to_hand</t>
         </is>
       </c>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>气郁质、特禀质</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>银翘散蓝图</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>抽牌直到手牌达到5张。消耗。</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>桔梗苦辛平，宣肺利咽，祛痰排脓。</t>
         </is>
       </c>
     </row>
@@ -1082,7 +1167,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1095,36 +1180,44 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F11" s="2" t="n">
-        <v>0</v>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>复制自身一个正面状态。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/75.png</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>阿是穴以痛为腧。</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
           <t>copy_buff_exhaust</t>
         </is>
       </c>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>特禀质</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>复制自身一个正面状态。消耗。</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>阿是穴以痛为腧。</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1139,7 +1232,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1149,39 +1242,47 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>2</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>yin_block_scaling</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>获得5点格挡。每有1层滋阴，额外获得1点格挡。</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>/assets/cards_player/17.png</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>鳖甲咸微寒，滋阴潜阳，退热除蒸，软坚散结。</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>yin_block_scaling</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr"/>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1196,7 +1297,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1209,36 +1310,40 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F13" s="2" t="n">
-        <v>3</v>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>block_echo_power</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
           <t>(能力)每当你获得格挡时，获得等量护盾。</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>/assets/cards_replacement_placeholders/buzhongyiqi.svg</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>熟地黄甘微温，补血滋阴，益精填髓。</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>block_echo_power</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>气虚质</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1253,7 +1358,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1266,178 +1371,186 @@
           <t>普通</t>
         </is>
       </c>
-      <c r="F14" s="2" t="n">
-        <v>1</v>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>自身</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>draw_discard</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
           <t>抽2张牌，丢弃1张牌。</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>/assets/cards_player/1.png</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>陈皮辛苦温，理气健脾，燥湿化痰。</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>draw_discard</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>平和质、痰湿质、气郁质</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>chuanxiong</t>
+          <t>chongrenbugu</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>川芎行气</t>
+          <t>冲任不固</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>造成5点伤害，抽1张牌。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/9.png</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>川芎辛温，活血行气，祛风止痛。</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>damage_draw</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr"/>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>平和质、血瘀质、气郁质</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>酸枣仁汤蓝图</t>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>(敌方技能)使玩家失去所有正面状态。</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>冲任气血亏虚，固摄无权。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>chuanxiongcha</t>
+          <t>chuanxiong</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>薄荷</t>
+          <t>川芎行气</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>本回合你的卡牌消耗减少1点（最低为0）。消耗。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/chuanxiongcha.svg</t>
+          <t>damage_draw</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>薄荷辛凉，疏散风热，清利头目，利咽透疹。</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>cost_reduction_turn</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>阳虚质、血瘀质、特禀质</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>银翘散蓝图</t>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>造成5点伤害，抽1张牌。</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>川芎辛温，活血行气，祛风止痛。</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>dachengqi</t>
+          <t>chuanxiongcha</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>莪术</t>
+          <t>薄荷</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1445,51 +1558,59 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F17" s="2" t="n">
-        <v>0</v>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>对一个敌人造成其当前生命值30%的伤害。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/dachengqi.svg</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>莪术辛苦温，破血行气，消积止痛。</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>percent_damage</t>
-        </is>
-      </c>
+          <t>cost_reduction_turn</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>阳虚质、湿热质、血瘀质</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>本回合你的卡牌消耗减少1点（最低为0）。消耗。</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>薄荷辛凉，疏散风热，清利头目，利咽透疹。</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>dahuang</t>
+          <t>dachengqi</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>大黄攻下</t>
+          <t>莪术</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1499,111 +1620,131 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>造成 12 点伤害，给予敌人 2 层“泄下”。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/32.png</t>
+          <t>percent_damage</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>大黄苦寒，泻下攻积，清热泻火。</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>dahuang_effect</t>
-        </is>
-      </c>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>阳虚质、湿热质、血瘀质</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>对一个敌人造成其当前生命值30%的伤害。消耗。</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>莪术辛苦温，破血行气，消积止痛。</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>danggui</t>
+          <t>dahuang</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>当归补血</t>
+          <t>大黄攻下</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>1</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>恢复 5 点生命。如果生命已满，改为获得 5 点护盾。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/34.png</t>
+          <t>dahuang_effect</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>当归甘辛温，补血活血，调经止痛。</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>danggui_effect</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>平和质</t>
-        </is>
-      </c>
+      <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>造成 12 点伤害，给予敌人 2 层“泄下”。</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>大黄苦寒，泻下攻积，清热泻火。</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>dangshen</t>
+          <t>danggui</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>党参补气</t>
+          <t>当归补血</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1613,116 +1754,132 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>获得4点格挡。下回合第一张技能卡效果+2。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/25.png</t>
+          <t>danggui_effect</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>党参甘平，补中益气，健脾益肺。</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>block_next_skill_bonus</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>气虚质</t>
-        </is>
-      </c>
+      <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>恢复 5 点生命。如果生命已满，改为获得 5 点护盾。</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>当归甘辛温，补血活血，调经止痛。</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>danshen</t>
+          <t>dangshen</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>三棱</t>
+          <t>党参补气</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>造成7点伤害。给予目标1层血瘀。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/danshen.svg</t>
+          <t>block_next_skill_bonus</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>三棱苦辛平，破血行气，消积止痛。</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>damage_debuff_stasis</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>血瘀质</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>获得4点格挡。下回合第一张技能卡效果+2。</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>党参甘平，补中益气，健脾益肺。</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>dazao</t>
+          <t>danshen</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>大枣养血</t>
+          <t>三棱</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -1730,55 +1887,59 @@
           <t>普通</t>
         </is>
       </c>
-      <c r="F22" s="2" t="n">
-        <v>0</v>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>恢复2点生命，获得2点格挡。消耗。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/26.png</t>
+          <t>damage_debuff_stasis</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>大枣甘温，补中益气，养血安神。</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>heal_block_exhaust</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr"/>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>平和质、气虚质、阳虚质、气郁质</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>葛根汤蓝图、小柴胡汤蓝图</t>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>造成7点伤害。给予目标1层血瘀。</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>三棱苦辛平，破血行气，消积止痛。</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>fangfeng</t>
+          <t>dazao</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>防风祛风</t>
+          <t>大枣养血</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1788,709 +1949,741 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>1</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>获得7点格挡。赋予一个敌人易伤。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/27.png</t>
+          <t>heal_block_exhaust</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>防风辛甘微温，祛风解表，胜湿止痛。</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>block_apply_vulnerable</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>气虚质、痰湿质</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>恢复2点生命，获得2点格挡。消耗。</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>大枣甘温，补中益气，养血安神。</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>fuling</t>
+          <t>equipment_bianzheng</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>茯苓渗湿</t>
+          <t>辨证论治</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>获得5点格挡。抽1张牌。消耗1层自身湿邪(如有)。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/28.png</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>茯苓甘淡平，利水渗湿，健脾宁心。</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>block_draw_cleanse_damp</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr"/>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>痰湿质</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>半夏厚朴汤蓝图、四君子汤蓝图、真武汤蓝图、酸枣仁汤蓝图</t>
+          <t>equipment_bianzheng</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr"/>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：回合开始自动择策，低血回复，否则补盾或得临时力量。</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>同病异治，因人、因时、因势而动。</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>fuzi</t>
+          <t>equipment_jingluo</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>附子回阳</t>
+          <t>经络学说</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>3</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>获得1点力量和1点敏捷，获得5点格挡。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/33.png</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>附子辛甘大热，回阳救逆，补火助阳。</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>strength_dex_block</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr"/>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>阳虚质</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>真武汤蓝图</t>
+          <t>equipment_jingluo</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr"/>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：每回合第一次打出技能牌时获得2点格挡。</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>经络通畅，则气血运行有序。</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>gancao</t>
+          <t>equipment_qiji</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>甘草和中</t>
+          <t>气机升降</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>恢复4点生命，抽1张牌。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/23.png</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>甘草甘平，补脾益气，调和诸药。</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>heal_draw</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr"/>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>平和质、气虚质</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>葛根汤蓝图、麻杏石甘汤蓝图、小柴胡汤蓝图、理中丸蓝图、四君子汤蓝图、小青龙汤蓝图、酸枣仁汤蓝图、麻黄汤蓝图、银翘散蓝图</t>
+          <t>equipment_qiji</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr"/>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：回合开始清除1个负面状态，若成功则恢复1点生命。</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>升降出入有常，气机通畅则百脉和。</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>guasha</t>
+          <t>equipment_qixue_jinye</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>刮痧：大椎</t>
+          <t>气血津液</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>1</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>移除自身所有热邪和寒邪。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/71.png</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>大椎穴为督脉要穴，诸阳之会。</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>cleanse_heat_cold</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr"/>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>湿热质、气郁质</t>
-        </is>
-      </c>
+          <t>equipment_qixue_jinye</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr"/>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：每获得5点格挡就恢复1点生命，单次最多恢复2点。</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>气血津液互生互化，方能濡养周身。</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>guipi</t>
+          <t>equipment_tianren</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>淡豆豉</t>
+          <t>天人相应</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>恢复20点生命，并抽2张牌。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/guipi.svg</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>淡豆豉苦辛凉，解表除烦，宣发郁热。</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>heal_draw</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr"/>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>气虚质、特禀质</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>银翘散蓝图</t>
+          <t>equipment_tianren</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：奇数玩家回合攻击+1，偶数玩家回合开始恢复2点生命。</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>顺应昼夜节律，借时气调身心。</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>guizhi</t>
+          <t>equipment_yinyang</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>桂枝通络</t>
+          <t>阴阳学说</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>获得3点格挡，本回合你的攻击卡无视敌人3点格挡。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/7.png</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>桂枝辛甘温，发汗解肌，温通经脉。</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>block_pierce_buff</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr"/>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>平和质、气虚质、阳虚质、血瘀质</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>葛根汤蓝图、小青龙汤蓝图、麻黄汤蓝图</t>
+          <t>equipment_yinyang</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：半血以上格挡+1，半血以下攻击+1；每场战斗免疫第一次眩晕。</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>阴阳互根，偏盛偏衰皆可调衡。</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>guizhitang</t>
+          <t>equipment_zangxiang</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>桂枝汤</t>
+          <t>藏象学说</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>2</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>恢复8点生命，获得5点格挡。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/37.png</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>桂枝汤，解肌发表，调和营卫。</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>heal_block</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr"/>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>气郁质</t>
-        </is>
-      </c>
+          <t>equipment_zangxiang</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：每回合结束积1层脏腑精气，满3层清空并恢复4点生命。</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>脏腑有别而相互为用，气化周流不息。</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>hegu</t>
+          <t>equipment_zhengti</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>点穴：合谷</t>
+          <t>整体观念</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>使一个敌人虚弱2回合。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/73.png</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>合谷穴镇静止痛，清热解表。</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>apply_weak</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr"/>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>痰湿质、血瘀质、气郁质、特禀质</t>
-        </is>
-      </c>
+          <t>equipment_zhengti</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr"/>
       <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：受到生命伤害时减免1点，治疗效果+1。</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>观其全局而后治其偏，身心内外同调。</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>huanglian</t>
+          <t>equipment_zhengxie</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>黄连燥湿</t>
+          <t>正邪相争</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>造成6点伤害，并清除目标1层正面状态。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/36.png</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>黄连苦寒，清热燥湿，泻火解毒。</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>damage_cleanse_buff</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr"/>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>平和质、湿热质</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>交泰丸蓝图</t>
+          <t>equipment_zhengxie</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：敌方攻击造成生命伤害后获得1层正气，最多3层；每层使格挡+1。</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>正气存内，邪不可干。</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>huanglianjiedu</t>
+          <t>equipment_zhiweibing</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>牛蒡子</t>
+          <t>治未病</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成10点伤害，并清除其所有正面状态。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/huanglianjiedu.svg</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>牛蒡子辛苦寒，疏散风热，宣肺利咽，解毒消肿。</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>aoe_damage_cleanse_all_buffs</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr"/>
-      <c r="L33" s="2" t="inlineStr">
-        <is>
-          <t>湿热质</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr">
-        <is>
-          <t>银翘散蓝图</t>
+          <t>equipment_zhiweibing</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：每场战斗开始获得5点格挡。全局被动生效。</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>预防为主，病未成而先护其正。</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>huangqi</t>
+          <t>equipment_ziwuliuzhu</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>黄芪固表</t>
+          <t>子午流注</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>装备</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="n">
-        <v>2</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>获得 10 点护盾。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/21.png</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>黄芪甘微温，补气升阳，益卫固表。</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>block</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr"/>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>平和质、气虚质</t>
-        </is>
-      </c>
+          <t>equipment_ziwuliuzhu</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>装备牌：非首回合的玩家回合开始额外抽1张牌。</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>按时取穴，借时令流转调节气血。</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>huangqin</t>
+          <t>fangfeng</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>黄芩清肺</t>
+          <t>防风祛风</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2500,63 +2693,67 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>药方配伍药材，占位牌。当前只用于药方完整配方合成。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_herb_placeholders/huangqin.svg</t>
+          <t>block_apply_vulnerable</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>黄芩苦寒，清热燥湿，泻火解毒，止血安胎。</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>formula_ingredient_placeholder</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>小柴胡汤蓝图</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>获得7点格挡。赋予一个敌人易伤。</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>防风辛甘微温，祛风解表，胜湿止痛。</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>huoxiang</t>
+          <t>fenghanshubiao</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>苏叶</t>
+          <t>风寒束表</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -2564,55 +2761,55 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F36" s="2" t="n">
-        <v>0</v>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>清除所有负面状态，并恢复10点生命。消耗。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/huoxiang.svg</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>苏叶辛温，解表散寒，行气和胃。</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>cleanse_self_heal</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr"/>
-      <c r="L36" s="2" t="inlineStr">
-        <is>
-          <t>痰湿质</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>半夏厚朴汤蓝图</t>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>(敌方技能)对玩家施加寒邪与虚弱。</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>风寒之邪侵袭肌表。</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>jinkui</t>
+          <t>formula_placeholder_01</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>柴胡</t>
+          <t>葛根汤</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2625,55 +2822,63 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F37" s="2" t="n">
-        <v>0</v>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>获得3点力量和3点敏捷，恢复10点生命。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/jinkui.svg</t>
+          <t>formula_gegen_tang</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>柴胡苦辛微寒，和解表里，疏肝升阳。</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>strength_dex_heal</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>阳虚质</t>
-        </is>
-      </c>
+      <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>小柴胡汤蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>获得8点格挡，清除自身1个负面状态，抽1张牌。</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>主治风寒初起：无汗恶寒、发热头痛、脖子痛、咽痛；功效：发汗解表、升津舒筋、散寒利咽。</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>jinyinhua</t>
+          <t>formula_placeholder_02</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>金银花露</t>
+          <t>麻杏石甘汤</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2683,119 +2888,135 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成3点伤害，并清除每个敌人的1层正面状态。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/6.png</t>
+          <t>formula_maxing_shigan_tang</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>金银花甘寒，清热解毒，疏散风热。</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>aoe_damage_cleanse</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质、湿热质</t>
-        </is>
-      </c>
+      <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>银翘散蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>对单体造成10点伤害，并施加2层热邪。</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>主治肺热证：怕热、出汗、咳嗽偶有痰；功效：辛凉宣泄、清肺平喘。</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>lianqiao</t>
+          <t>formula_placeholder_03</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>连翘解毒</t>
+          <t>小柴胡汤</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成4点伤害，并清除1层热邪。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/44.png</t>
+          <t>formula_xiaochaihu_tang</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>连翘苦微寒，清热解毒，消肿散结。</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>aoe_damage_cleanse_heat</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质、湿热质</t>
-        </is>
-      </c>
+      <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>银翘散蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>恢复6点生命，抽2张牌，清除自身1个负面状态。</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>主治少阳证：头晕心烦、恶心、情绪低落、不思饮食；功效：和解少阳、疏肝和胃、调畅气机。</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>liuwei</t>
+          <t>formula_placeholder_04</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>五味子</t>
+          <t>理中丸</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2808,55 +3029,63 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F40" s="2" t="n">
-        <v>0</v>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>获得5层滋阴和5点格挡。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/liuwei.svg</t>
+          <t>formula_lizhong_wan</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>五味子酸甘温，收敛固涩，益气生津，补肾宁心。</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>yin_block</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
-      <c r="L40" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质</t>
-        </is>
-      </c>
+      <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>小青龙汤蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>恢复8点生命，获得1点力量。</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>主治脾胃虚寒：四肢冰凉、食欲差、轻度腹胀、大便稀；功效：温中祛寒、补气健脾。</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>longdan</t>
+          <t>formula_placeholder_05</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>人参</t>
+          <t>半夏厚朴汤</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2869,121 +3098,137 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F41" s="2" t="n">
-        <v>0</v>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>对一个敌人造成20点真实伤害。消耗。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/longdan.svg</t>
+          <t>formula_banxia_houpu_tang</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>人参甘微苦微温，大补元气，复脉固脱，补脾益肺，生津养血。</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>true_damage</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质、湿热质、血瘀质</t>
-        </is>
-      </c>
+      <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>小柴胡汤蓝图、理中丸蓝图、四君子汤蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>对单体造成8点伤害，施加2回合虚弱；若目标有痰湿禁锢或湿邪，额外抽1张。</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>主治梅核气：咽喉异物感、吐不出咽不下；功效：行气散结、降逆化痰。</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>mahuang</t>
+          <t>formula_placeholder_06</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>麻黄发汗</t>
+          <t>交泰丸</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>造成 8 点伤害。如果敌人有“寒邪”，额外造成 4 点伤害。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/31.png</t>
+          <t>formula_jiaotai_wan</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>麻黄辛微苦温，发汗解表，宣肺平喘。</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>mahuang_effect</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>平和质、阳虚质</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>葛根汤蓝图、麻杏石甘汤蓝图、小青龙汤蓝图、麻黄汤蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>获得6点格挡，清除自身1个负面状态。消耗。</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>主治心肾不交失眠：入睡难、易惊醒、醒后难再睡；功效：交通心肾、安神助眠。</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>mahuangtang</t>
+          <t>formula_placeholder_07</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>细辛</t>
+          <t>四君子汤</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -2991,117 +3236,129 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F43" s="2" t="n">
-        <v>0</v>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>本回合攻击卡无视敌人所有格挡。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/mahuangtang.svg</t>
+          <t>formula_sijunzi_tang</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>细辛辛温，解表散寒，祛风止痛，通窍温肺。</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>attack_pierce_all</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr"/>
-      <c r="L43" s="2" t="inlineStr">
-        <is>
-          <t>阳虚质、血瘀质</t>
-        </is>
-      </c>
+      <c r="L43" s="2" t="inlineStr"/>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>小青龙汤蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>恢复10点生命，获得6点格挡。</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>主治脾胃气虚：神疲乏力、少气懒言、食欲不振、大便偏稀；功效：益气健脾、补益中气。</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>maidong</t>
+          <t>formula_placeholder_08</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>麦冬滋阴</t>
+          <t>真武汤</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>获得2层滋阴。抽1张牌。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/11.png</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="inlineStr">
-        <is>
-          <t>麦冬甘微苦微寒，滋阴润肺，益胃生津。</t>
-        </is>
-      </c>
-      <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>buff_yin</t>
-        </is>
-      </c>
+          <t>formula_zhenwu_tang</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
-      <c r="L44" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>本场战斗格挡效果 +50%，回合开始获得1点格挡。</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>主治脾肾阳虚、水气内停：小便不利、四肢沉重肿痛、腹痛下利、肢体浮肿；功效：温阳利水、温补脾肾化湿。</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>mingmen</t>
+          <t>formula_placeholder_09</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>雷火灸：命门</t>
+          <t>小青龙汤</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -3109,56 +3366,68 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F45" s="2" t="n">
-        <v>3</v>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>获得3点力量和5点格挡。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/74.png</t>
+          <t>formula_xiaoqinglong_tang</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>命门穴温补肾阳。</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>strength_block</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>阳虚质、血瘀质</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>对所有敌人造成7点伤害；若目标有寒邪，额外3点伤害。</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>主治外寒内饮：恶寒发热、无汗身痛、咳喘痰多清稀、胸闷浮肿；功效：解表散寒、温肺化饮。</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>qinggusan</t>
+          <t>formula_placeholder_10</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>杏仁</t>
+          <t>酸枣仁汤</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
@@ -3166,60 +3435,68 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F46" s="2" t="n">
-        <v>0</v>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>造成8点伤害。消耗3层滋阴使伤害翻倍。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/qinggusan.svg</t>
+          <t>formula_suanzaoren_tang</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>杏仁苦微温，降气止咳，平喘润肠。</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>yin_spend_double_damage</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr"/>
-      <c r="L46" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质、湿热质</t>
-        </is>
-      </c>
+      <c r="L46" s="2" t="inlineStr"/>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>麻杏石甘汤蓝图、麻黄汤蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>使一个敌人困倦1回合，恢复5点生命。</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>主治肝血不足、虚热扰神：虚烦失眠、心悸盗汗、头晕目眩；功效：养血安神、清热除烦。</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>qingying</t>
+          <t>formula_placeholder_11</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>蒲公英</t>
+          <t>麻黄汤</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -3227,51 +3504,59 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F47" s="2" t="n">
-        <v>0</v>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>清除场上所有热邪，每清除1层对所有敌人造成2点伤害。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/qingying.svg</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="inlineStr">
-        <is>
-          <t>蒲公英苦甘寒，清热解毒，消肿散结，利湿通淋。</t>
-        </is>
-      </c>
-      <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>cleanse_heat_aoe_damage</t>
-        </is>
-      </c>
+          <t>formula_mahuang_tang</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>阴虚质、湿热质</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>本回合攻击无视格挡，抽1张牌。消耗。</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>主治太阳伤寒：发热、无汗、恶寒怕冷；功效：发汗解表、宣肺平喘。</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>rougui</t>
+          <t>formula_placeholder_12</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>肉桂引火</t>
+          <t>银翘散</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药方</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3281,120 +3566,136 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>获得3点力量。本回合结束时失去3点力量。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/45.png</t>
+          <t>formula_yinqiao_san</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>肉桂辛甘大热，补火助阳，引火归元。</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>strength_temp</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>阳虚质、血瘀质</t>
-        </is>
-      </c>
+      <c r="L48" s="2" t="inlineStr"/>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>交泰丸蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>对所有敌人造成6点伤害并施加1层热邪，清除敌人1层正面状态。</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>主治温病初起风热证：发热、微恶风寒、头痛口渴、咳嗽咽痛；功效：辛凉解表、清热解毒、疏散风热。</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>sanqi</t>
+          <t>fuling</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>三七化瘀</t>
+          <t>茯苓渗湿</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>0</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>造成5点伤害。如果目标有血瘀，则额外造成5点伤害。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/39.png</t>
+          <t>block_draw_cleanse_damp</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>三七甘微苦温，散瘀止血，消肿定痛。</t>
-        </is>
-      </c>
-      <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>damage_conditional_stasis</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>血瘀质</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>获得5点格挡。抽1张牌。消耗1层自身湿邪(如有)。</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>茯苓甘淡平，利水渗湿，健脾宁心。</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>sanyinjiao</t>
+          <t>fuzi</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>温针灸：三阴交</t>
+          <t>附子回阳</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -3402,222 +3703,258 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F50" s="2" t="n">
-        <v>1</v>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>(能力)回合结束时若有格挡，则格挡不消失。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/72.png</t>
+          <t>strength_dex_block</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>三阴交为足三阴经交会穴。</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>retain_block_power</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>痰湿质</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>获得1点力量和1点敏捷，获得5点格挡。消耗。</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>附子辛甘大热，回阳救逆，补火助阳。</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>shanyao</t>
+          <t>gancao</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>山药平补</t>
+          <t>甘草和中</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>2</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>(能力)回合结束时恢复2点生命。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/24.png</t>
+          <t>heal_draw</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>山药甘平，补脾养胃，生津益肺。</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>end_turn_heal_power</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr"/>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>平和质、气虚质</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>恢复4点生命，抽1张牌。</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>甘草甘平，补脾益气，调和诸药。</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>shanyurou</t>
+          <t>ganhuowang</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>山萸肉固涩</t>
+          <t>肝火旺</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>恢复3点生命，并额外恢复等同于滋阴层数的生命值。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/19.png</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr">
-        <is>
-          <t>山茱萸酸涩微温，补益肝肾，收涩固脱。</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>yin_heal_scaling</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr"/>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质</t>
-        </is>
-      </c>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr"/>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr"/>
       <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>(敌方能力)每回合开始，自身攻击力+2。</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>肝气郁结，日久化火。</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>shanzha</t>
+          <t>guasha</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>山楂消食</t>
+          <t>刮痧：大椎</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>造成3点伤害，获得5点格挡。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/3.png</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>山楂酸甘微温，消食健胃，行气散瘀。</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>damage_block</t>
-        </is>
-      </c>
+          <t>cleanse_heat_cold</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr"/>
+      <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>平和质、气虚质</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>移除自身所有热邪和寒邪。</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>大椎穴为督脉要穴，诸阳之会。</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>shengdi</t>
+          <t>guipi</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>生地凉血</t>
+          <t>淡豆豉</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3627,54 +3964,70 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>2</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>获得4层滋阴。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/12.png</t>
+          <t>heal_draw</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>生地黄甘苦寒，清热凉血，养阴生津。</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>yin_gain_exhaust</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>阴虚质、湿热质</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>恢复20点生命，并抽2张牌。消耗。</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>淡豆豉苦辛凉，解表除烦，宣发郁热。</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>shengjiang</t>
+          <t>guizhi</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>生姜发散</t>
+          <t>桂枝通络</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3687,222 +4040,254 @@
           <t>普通</t>
         </is>
       </c>
-      <c r="F55" s="2" t="n">
-        <v>0</v>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>本回合，你的下一张攻击卡额外造成3点伤害。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/5.png</t>
+          <t>block_pierce_buff</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>生姜辛微温，解表散寒，温中止呕。</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>buff_attack</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr"/>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>阳虚质、血瘀质</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>葛根汤蓝图、小柴胡汤蓝图、半夏厚朴汤蓝图、真武汤蓝图</t>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>获得3点格挡，本回合你的攻击卡无视敌人3点格挡。</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>桂枝辛甘温，发汗解肌，温通经脉。</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>shengma</t>
+          <t>hegu</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>升麻升提</t>
+          <t>点穴：合谷</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>1</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>本回合每次获得格挡，获得1点临时力量。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/29.png</t>
+          <t>apply_weak</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>升麻辛微甘微寒，升举阳气。</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>block_to_strength</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>使一个敌人虚弱2回合。</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>合谷穴镇静止痛，清热解表。</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>shenmen</t>
+          <t>huanglian</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>耳穴：神门</t>
+          <t>黄连燥湿</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>0</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>获得5点格挡。本回合敌人第一次伤害减少3点。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/70.png</t>
+          <t>damage_cleanse_buff</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>神门穴宁心安神。</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>block_reduce_next_damage</t>
-        </is>
-      </c>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>痰湿质、气郁质、特禀质</t>
-        </is>
-      </c>
+      <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>造成6点伤害，并清除目标1层正面状态。</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>黄连苦寒，清热燥湿，泻火解毒。</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>shihu</t>
+          <t>huanglianjiedu</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>石斛益胃</t>
+          <t>牛蒡子</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>获得1层滋阴。本场战斗中，滋阴层数上限+2。消耗。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/18.png</t>
+          <t>aoe_damage_cleanse_all_buffs</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>石斛甘微寒，益胃生津，滋阴清热。</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>yin_cap_increase</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>阴虚质</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>对所有敌人造成10点伤害，并清除其所有正面状态。消耗。</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>牛蒡子辛苦寒，疏散风热，宣肺利咽，解毒消肿。</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>sijunzi</t>
+          <t>huangqi</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>天门冬</t>
+          <t>黄芪固表</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3912,115 +4297,123 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>恢复15点生命，并获得5点格挡。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/sijunzi.svg</t>
+          <t>block</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>天门冬甘苦寒，养阴润燥，清肺生津。</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>heal_block</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>气虚质、痰湿质</t>
-        </is>
-      </c>
+      <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>获得 10 点护盾。</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>黄芪甘微温，补气升阳，益卫固表。</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>suanzaoren</t>
+          <t>huangqin</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>酸枣仁安眠</t>
+          <t>黄芩清肺</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>0</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>使一个敌人获得1层困倦（下回合跳过行动）。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/41.png</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>酸枣仁甘酸平，养心益肝，安神。</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>sleep_debuff</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr"/>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>痰湿质、气郁质、特禀质</t>
-        </is>
-      </c>
+          <t>formula_ingredient_placeholder</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr"/>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>酸枣仁汤蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>药方配伍药材，占位牌。当前只用于药方完整配方合成。</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>黄芩苦寒，清热燥湿，泻火解毒，止血安胎。</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>tuina</t>
+          <t>huoxiang</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>推拿：捏脊</t>
+          <t>苏叶</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4030,54 +4423,66 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>移除自身2个负面状态，抽1张牌。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/68.png</t>
+          <t>cleanse_self_heal</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>捏脊疗法可调和阴阳，疏通经络。</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>cleanse_two_draw</t>
-        </is>
-      </c>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>气郁质、特禀质</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>清除所有负面状态，并恢复10点生命。消耗。</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>苏叶辛温，解表散寒，行气和胃。</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>wumei</t>
+          <t>jinkui</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>荆芥穗</t>
+          <t>柴胡</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4090,177 +4495,197 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F62" s="2" t="n">
-        <v>0</v>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>偷取一个敌人所有正面状态。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/wumei.svg</t>
+          <t>strength_dex_heal</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>荆芥穗辛微温，解表散风，透疹消疮。</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>steal_buffs</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>特禀质</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>银翘散蓝图</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>获得3点力量和3点敏捷，恢复10点生命。消耗。</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>柴胡苦辛微寒，和解表里，疏肝升阳。</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>xiaochaihu</t>
+          <t>jinyinhua</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>葛根</t>
+          <t>金银花露</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="n">
-        <v>2</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>恢复5点生命，抽2张牌，获得4点格挡。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/xiaochaihu.svg</t>
+          <t>aoe_damage_cleanse</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>葛根甘辛凉，解肌退热，生津止渴，升阳止泻。</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>heal_draw_block</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>平和质、气郁质</t>
-        </is>
-      </c>
+      <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>葛根汤蓝图</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>对所有敌人造成3点伤害，并清除每个敌人的1层正面状态。</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>金银花甘寒，清热解毒，疏散风热。</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>xiaoyao</t>
+          <t>lianqiao</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>赤芍</t>
+          <t>连翘解毒</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>清除所有负面状态，抽3张牌。消耗。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/xiaoyao.svg</t>
+          <t>aoe_damage_cleanse_heat</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>赤芍苦微寒，清热凉血，散瘀止痛。</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>cleanse_draw</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>气郁质、特禀质</t>
-        </is>
-      </c>
+      <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>葛根汤蓝图</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>对所有敌人造成4点伤害，并清除1层热邪。</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>连翘苦微寒，清热解毒，消肿散结。</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>xuanshen</t>
+          <t>liuwei</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>玄参泻火</t>
+          <t>五味子</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4270,54 +4695,70 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>消耗所有滋阴。每消耗1层，对随机敌人造成3点伤害。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/14.png</t>
+          <t>yin_block</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>玄参苦咸微寒，清热凉血，泻火解毒，滋阴。</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>yin_spend_damage_random</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>阴虚质、湿热质</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>获得5层滋阴和5点格挡。消耗。</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>五味子酸甘温，收敛固涩，益气生津，补肾宁心。</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>xuefu</t>
+          <t>longdan</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>厚朴</t>
+          <t>人参</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4330,55 +4771,63 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F66" s="2" t="n">
-        <v>0</v>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>清除所有敌人正面状态。消耗。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/xuefu.svg</t>
+          <t>true_damage</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>厚朴苦辛温，燥湿消痰，下气除满。</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>cleanse_enemy_buffs</t>
-        </is>
-      </c>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>血瘀质</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>半夏厚朴汤蓝图</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>对一个敌人造成20点真实伤害。消耗。</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>人参甘微苦微温，大补元气，复脉固脱，补脾益肺，生津养血。</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>yinqiao</t>
+          <t>mahuang</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>生石膏</t>
+          <t>麻黄发汗</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4388,115 +4837,127 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="n">
-        <v>0</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成8点伤害，并施加1层热邪。消耗。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/yinqiao.svg</t>
+          <t>mahuang_effect</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>生石膏甘辛大寒，清热泻火，除烦止渴。</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>aoe_damage_heat</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>湿热质</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>麻杏石甘汤蓝图</t>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>造成 8 点伤害。如果敌人有“寒邪”，额外造成 4 点伤害。</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>麻黄辛微苦温，发汗解表，宣肺平喘。</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>yiyi</t>
+          <t>mahuangtang</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>薏苡除湿</t>
+          <t>细辛</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>获得4点格挡，并移除自身的1个负面状态。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/4.png</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>薏苡仁甘淡凉，利水渗湿，健脾止泻。</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>block_cleanse_self</t>
-        </is>
-      </c>
+          <t>attack_pierce_all</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr"/>
+      <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>平和质、气虚质、痰湿质</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>本回合攻击卡无视敌人所有格挡。消耗。</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>细辛辛温，解表散寒，祛风止痛，通窍温肺。</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>yupingfeng</t>
+          <t>maidong</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>竹叶</t>
+          <t>麦冬滋阴</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4506,63 +4967,67 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>获得20点格挡。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/yupingfeng.svg</t>
+          <t>buff_yin</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>竹叶甘辛淡寒，清热除烦，生津利尿。</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>block</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>气虚质</t>
-        </is>
-      </c>
+      <c r="L69" s="2" t="inlineStr"/>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>银翘散蓝图</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>获得2层滋阴。抽1张牌。</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>麦冬甘微苦微寒，滋阴润肺，益胃生津。</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>yuzhu</t>
+          <t>mingmen</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>玉竹生津</t>
+          <t>雷火灸：命门</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
@@ -4570,113 +5035,129 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F70" s="2" t="n">
-        <v>2</v>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>(能力)回合开始时若有滋阴，获得1点真气。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/15.png</t>
+          <t>strength_block</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>玉竹甘微寒，养阴润燥，生津止渴。</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>yin_power_energy</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>阴虚质</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>获得3点力量和5点格挡。</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>命门穴温补肾阳。</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>zexie</t>
+          <t>pixushikun</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>泽泻利水</t>
+          <t>脾虚湿困</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>移除自身所有湿邪，每层获得2点格挡。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/42.png</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>泽泻甘淡寒，利水渗湿，泄热。</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>cleanse_damp_convert_block</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr"/>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>痰湿质、气郁质</t>
-        </is>
-      </c>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr"/>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr"/>
       <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>(敌方能力)玩家卡牌消耗增加1点。</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>脾气虚弱，运化失职。</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>zhenwu</t>
+          <t>qinggusan</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>苍术</t>
+          <t>杏仁</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
@@ -4684,51 +5165,59 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F72" s="2" t="n">
-        <v>0</v>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>本场战斗中，你的格挡效果翻倍。消耗。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_replacement_placeholders/zhenwu.svg</t>
+          <t>yin_spend_double_damage</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>苍术辛苦温，燥湿健脾，祛风散寒，明目。</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>double_block_buff</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>阳虚质、痰湿质</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>造成8点伤害。消耗3层滋阴使伤害翻倍。</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>杏仁苦微温，降气止咳，平喘润肠。</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>zhimu</t>
+          <t>qingying</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>知母清热</t>
+          <t>蒲公英</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4738,115 +5227,123 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="n">
-        <v>1</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>获得1层滋阴。本回合你的攻击卡额外施加1层虚热。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/13.png</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>知母苦甘寒，清热泻火，滋阴润燥。</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>yin_attack_virtual_heat</t>
-        </is>
-      </c>
+          <t>cleanse_heat_aoe_damage</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr"/>
+      <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>阴虚质、湿热质</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>酸枣仁汤蓝图</t>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>清除场上所有热邪，每清除1层对所有敌人造成2点伤害。消耗。</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>蒲公英苦甘寒，清热解毒，消肿散结，利湿通淋。</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>zhishi</t>
+          <t>qizhixueyu</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>枳实行气</t>
+          <t>气滞血瘀</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>抽1张牌。如果本回合已打出攻击牌，额外抽1张。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/43.png</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>枳实苦辛酸微寒，破气消积。</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>draw_if_attack</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr"/>
-      <c r="L74" s="2" t="inlineStr">
-        <is>
-          <t>痰湿质、血瘀质、气郁质</t>
-        </is>
-      </c>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr"/>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>(敌方能力)玩家每打出一张牌受到1点伤害。</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>气机郁滞，血行不畅。</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>zhusha</t>
+          <t>reruyingxue</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>朱砂安神</t>
+          <t>热入营血</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4859,51 +5356,55 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F75" s="2" t="n">
-        <v>1</v>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>(能力)攻击卡有25%几率使敌人眩晕。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/35.png</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>朱砂甘微寒，清心镇惊，安神解毒。</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>attack_stun_chance</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr"/>
-      <c r="L75" s="2" t="inlineStr">
-        <is>
-          <t>特禀质</t>
-        </is>
-      </c>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr"/>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr"/>
       <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>(敌方能力)回合结束时造成热邪层数的伤害。</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>温热病邪深入营分血分。</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>zouguan</t>
+          <t>rougui</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>拔罐：走罐</t>
+          <t>肉桂引火</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4913,116 +5414,136 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F76" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成5点伤害。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/69.png</t>
+          <t>strength_temp</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>走罐可行气活血，祛风散寒。</t>
-        </is>
-      </c>
-      <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>aoe_damage</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
-      <c r="L76" s="2" t="inlineStr">
-        <is>
-          <t>特禀质</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>获得3点力量。本回合结束时失去3点力量。</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>肉桂辛甘大热，补火助阳，引火归元。</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>zusanli</t>
+          <t>sanqi</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>针刺：足三里</t>
+          <t>三七化瘀</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>药材牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F77" s="2" t="n">
-        <v>2</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>(能力)每当你打出攻击卡时，每层恢复1点生命。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/66.png</t>
+          <t>damage_conditional_stasis</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>足三里为“强壮要穴”，健脾和胃。</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>zusanli_effect</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
-      <c r="L77" s="2" t="inlineStr">
-        <is>
-          <t>平和质、气虚质、特禀质</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>造成5点伤害。如果目标有血瘀，则额外造成5点伤害。</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>三七甘微苦温，散瘀止血，消肿定痛。</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_01</t>
+          <t>sanyinjiao</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>葛根汤</t>
+          <t>温针灸：三阴交</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -5030,100 +5551,120 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F78" s="2" t="n">
-        <v>1</v>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>获得8点格挡，清除自身1个负面状态，抽1张牌。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_formula_placeholders/gegen_tang.svg</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>主治风寒初起：无汗恶寒、发热头痛、脖子痛、咽痛；功效：发汗解表、升津舒筋、散寒利咽。</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>formula_gegen_tang</t>
-        </is>
-      </c>
+          <t>retain_block_power</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr"/>
+      <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>(能力)回合结束时若有格挡，则格挡不消失。</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>三阴交为足三阴经交会穴。</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_02</t>
+          <t>shanyao</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>麻杏石甘汤</t>
+          <t>山药平补</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="n">
-        <v>1</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>对单体造成10点伤害，并施加2层热邪。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_formula_placeholders/maxing_shigan_tang.svg</t>
+          <t>end_turn_heal_power</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>主治肺热证：怕热、出汗、咳嗽偶有痰；功效：辛凉宣泄、清肺平喘。</t>
-        </is>
-      </c>
-      <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>formula_maxing_shigan_tang</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>(能力)回合结束时恢复2点生命。</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>山药甘平，补脾养胃，生津益肺。</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_03</t>
+          <t>shanyurou</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>小柴胡汤</t>
+          <t>山萸肉固涩</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5133,108 +5674,132 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F80" s="2" t="n">
-        <v>1</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>恢复6点生命，抽2张牌，清除自身1个负面状态。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/10.png</t>
+          <t>yin_heal_scaling</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>主治少阳证：头晕心烦、恶心、情绪低落、不思饮食；功效：和解少阳、疏肝和胃、调畅气机。</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>formula_xiaochaihu_tang</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>恢复3点生命，并额外恢复等同于滋阴层数的生命值。</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>山茱萸酸涩微温，补益肝肾，收涩固脱。</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_04</t>
+          <t>shanzha</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>理中丸</t>
+          <t>山楂消食</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>技能</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="n">
-        <v>1</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>恢复8点生命，获得1点力量。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_formula_placeholders/lizhong_wan.svg</t>
+          <t>damage_block</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>主治脾胃虚寒：四肢冰凉、食欲差、轻度腹胀、大便稀；功效：温中祛寒、补气健脾。</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
         <is>
-          <t>formula_lizhong_wan</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>造成3点伤害，获得5点格挡。</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>山楂酸甘微温，消食健胃，行气散瘀。</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_05</t>
+          <t>shenbunaqi</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>半夏厚朴汤</t>
+          <t>肾不纳气</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
@@ -5242,47 +5807,55 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F82" s="2" t="n">
-        <v>1</v>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>对单体造成8点伤害，施加2回合虚弱；若目标有痰湿禁锢或湿邪，额外抽1张。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_formula_placeholders/banxia_houpu_tang.svg</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>主治梅核气：咽喉异物感、吐不出咽不下；功效：行气散结、降逆化痰。</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>formula_banxia_houpu_tang</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr"/>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr"/>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="L82" s="2" t="inlineStr"/>
       <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>(敌方技能)偷取玩家1点真气上限。</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>肾气虚衰，摄纳无权。</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_06</t>
+          <t>shengdi</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>交泰丸</t>
+          <t>生地凉血</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5292,50 +5865,66 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>获得6点格挡，清除自身1个负面状态。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_formula_placeholders/jiaotai_wan.svg</t>
+          <t>yin_gain_exhaust</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>主治心肾不交失眠：入睡难、易惊醒、醒后难再睡；功效：交通心肾、安神助眠。</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>formula_jiaotai_wan</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
-      <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>获得4层滋阴。消耗。</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>生地黄甘苦寒，清热凉血，养阴生津。</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_07</t>
+          <t>shengjiang</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>四君子汤</t>
+          <t>生姜发散</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5345,50 +5934,66 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F84" s="2" t="n">
-        <v>1</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>恢复10点生命，获得6点格挡。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/47.png</t>
+          <t>buff_attack</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>主治脾胃气虚：神疲乏力、少气懒言、食欲不振、大便偏稀；功效：益气健脾、补益中气。</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>formula_sijunzi_tang</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
-      <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>本回合，你的下一张攻击卡额外造成3点伤害。消耗。</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>生姜辛微温，解表散寒，温中止呕。</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_08</t>
+          <t>shengma</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>真武汤</t>
+          <t>升麻升提</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5398,103 +6003,127 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F85" s="2" t="n">
-        <v>2</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>本场战斗格挡效果 +50%，回合开始获得1点格挡。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/58.png</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>主治脾肾阳虚、水气内停：小便不利、四肢沉重肿痛、腹痛下利、肢体浮肿；功效：温阳利水、温补脾肾化湿。</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>formula_zhenwu_tang</t>
-        </is>
-      </c>
+          <t>block_to_strength</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr"/>
+      <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>本回合每次获得格挡，获得1点临时力量。</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>升麻辛微甘微寒，升举阳气。</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_09</t>
+          <t>shenmen</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>小青龙汤</t>
+          <t>耳穴：神门</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>能力</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F86" s="2" t="n">
-        <v>1</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成7点伤害；若目标有寒邪，额外3点伤害。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_formula_placeholders/xiaoqinglong_tang.svg</t>
+          <t>block_reduce_next_damage</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>主治外寒内饮：恶寒发热、无汗身痛、咳喘痰多清稀、胸闷浮肿；功效：解表散寒、温肺化饮。</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
         <is>
-          <t>formula_xiaoqinglong_tang</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>获得5点格挡。本回合敌人第一次伤害减少3点。</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>神门穴宁心安神。</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_10</t>
+          <t>shihu</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>酸枣仁汤</t>
+          <t>石斛益胃</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5504,55 +6133,71 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F87" s="2" t="n">
-        <v>1</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>使一个敌人困倦1回合，恢复5点生命。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_formula_placeholders/suanzaoren_tang.svg</t>
+          <t>yin_cap_increase</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>主治肝血不足、虚热扰神：虚烦失眠、心悸盗汗、头晕目眩；功效：养血安神、清热除烦。</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>formula_suanzaoren_tang</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
-      <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>获得1层滋阴。本场战斗中，滋阴层数上限+2。消耗。</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>石斛甘微寒，益胃生津，滋阴清热。</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_11</t>
+          <t>sijunzi</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>麻黄汤</t>
+          <t>天门冬</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>攻击</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E88" s="2" t="inlineStr">
@@ -5560,47 +6205,67 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F88" s="2" t="n">
-        <v>0</v>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>本回合攻击无视格挡，抽1张牌。消耗。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/46.png</t>
+          <t>heal_block</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>主治太阳伤寒：发热、无汗、恶寒怕冷；功效：发汗解表、宣肺平喘。</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
         <is>
-          <t>formula_mahuang_tang</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr"/>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>恢复15点生命，并获得5点格挡。消耗。</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>天门冬甘苦寒，养阴润燥，清肺生津。</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>formula_placeholder_12</t>
+          <t>suanzaoren</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>银翘散</t>
+          <t>酸枣仁安眠</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>药方牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5610,50 +6275,58 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F89" s="2" t="n">
-        <v>1</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>对所有敌人造成6点伤害并施加1层热邪，清除敌人1层正面状态。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/51.png</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>主治温病初起风热证：发热、微恶风寒、头痛口渴、咳嗽咽痛；功效：辛凉解表、清热解毒、疏散风热。</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>formula_yinqiao_san</t>
-        </is>
-      </c>
+          <t>sleep_debuff</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr"/>
+      <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>使一个敌人获得1层困倦（下回合跳过行动）。</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>酸枣仁甘酸平，养心益肝，安神。</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>equipment_bianzheng</t>
+          <t>tanmengxinqiao</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>辨证论治</t>
+          <t>痰蒙心窍</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5666,113 +6339,121 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F90" s="2" t="n">
-        <v>0</v>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>装备牌：回合开始自动择策，低血回复，否则补盾或得临时力量。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/bianzheng.webp</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>同病异治，因人、因时、因势而动。</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>equipment_bianzheng</t>
-        </is>
-      </c>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr"/>
+      <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>(敌方技能)使玩家眩晕1回合。</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>痰浊上蒙，阻闭清窍。</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>equipment_jingluo</t>
+          <t>tuina</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>经络学说</t>
+          <t>推拿：捏脊</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F91" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>装备牌：每回合第一次打出技能牌时获得2点格挡。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/jingluo.webp</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>经络通畅，则气血运行有序。</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>equipment_jingluo</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>cleanse_two_draw</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr"/>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>移除自身2个负面状态，抽1张牌。</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>捏脊疗法可调和阴阳，疏通经络。</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>equipment_qiji</t>
+          <t>wumei</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>气机升降</t>
+          <t>荆芥穗</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -5780,165 +6461,193 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F92" s="2" t="n">
-        <v>0</v>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>装备牌：回合开始清除1个负面状态，若成功则恢复1点生命。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/qiji.webp</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>升降出入有常，气机通畅则百脉和。</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>equipment_qiji</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>steal_buffs</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr"/>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>偷取一个敌人所有正面状态。消耗。</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>荆芥穗辛微温，解表散风，透疹消疮。</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>equipment_qixue_jinye</t>
+          <t>xiaochaihu</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>气血津液</t>
+          <t>葛根</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F93" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>装备牌：每获得5点格挡就恢复1点生命，单次最多恢复2点。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/qixue_jinye.webp</t>
+          <t>heal_draw_block</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>气血津液互生互化，方能濡养周身。</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>equipment_qixue_jinye</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>恢复5点生命，抽2张牌，获得4点格挡。</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>葛根甘辛凉，解肌退热，生津止渴，升阳止泻。</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>equipment_tianren</t>
+          <t>xiaoyao</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>天人相应</t>
+          <t>赤芍</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>装备牌：奇数玩家回合攻击+1，偶数玩家回合开始恢复2点生命。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/tianren.webp</t>
+          <t>cleanse_draw</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>顺应昼夜节律，借时气调身心。</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>equipment_tianren</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>清除所有负面状态，抽3张牌。消耗。</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>赤芍苦微寒，清热凉血，散瘀止痛。</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>equipment_yinyang</t>
+          <t>xinshenbujiao</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>阴阳学说</t>
+          <t>心肾不交</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -5951,165 +6660,181 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F95" s="2" t="n">
-        <v>0</v>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>装备牌：半血以上格挡+1，半血以下攻击+1；每场战斗免疫第一次眩晕。</t>
+          <t>单体</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/yinyang.webp</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>阴阳互根，偏盛偏衰皆可调衡。</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>equipment_yinyang</t>
-        </is>
-      </c>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
+      <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>(敌方技能)下回合无法获得格挡。</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>心火亢盛，肾水不足。</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>equipment_zangxiang</t>
+          <t>xuanshen</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>藏象学说</t>
+          <t>玄参泻火</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>装备牌：每回合结束积1层脏腑精气，满3层清空并恢复4点生命。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/zangxiang.webp</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>脏腑有别而相互为用，气化周流不息。</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>equipment_zangxiang</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>yin_spend_damage_random</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>消耗所有滋阴。每消耗1层，对随机敌人造成3点伤害。</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>玄参苦咸微寒，清热凉血，泻火解毒，滋阴。</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>equipment_zhengti</t>
+          <t>xuefu</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>整体观念</t>
+          <t>厚朴</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F97" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>装备牌：受到生命伤害时减免1点，治疗效果+1。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/zhengti.webp</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>观其全局而后治其偏，身心内外同调。</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>equipment_zhengti</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>cleanse_enemy_buffs</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>清除所有敌人正面状态。消耗。</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>厚朴苦辛温，燥湿消痰，下气除满。</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>equipment_zhengxie</t>
+          <t>yangmingfushi</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>正邪相争</t>
+          <t>阳明腑实</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -6122,170 +6847,194 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F98" s="2" t="n">
-        <v>0</v>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>装备牌：敌方攻击造成生命伤害后获得1层正气，最多3层；每层使格挡+1。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/zhengxie.webp</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>正气存内，邪不可干。</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>equipment_zhengxie</t>
-        </is>
-      </c>
+          <t>status_enemy</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
+      <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="L98" s="2" t="inlineStr"/>
       <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>(敌方能力)回合结束时清除玩家所有护盾。</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>邪热与腑实互结。</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>equipment_zhiweibing</t>
+          <t>yinqiao</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>治未病</t>
+          <t>生石膏</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
         <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="n">
-        <v>0</v>
+          <t>稀有</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>装备牌：每场战斗开始获得5点格挡。全局被动生效。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/zhiweibing.webp</t>
+          <t>aoe_damage_heat</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>预防为主，病未成而先护其正。</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
         <is>
-          <t>equipment_zhiweibing</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>对所有敌人造成8点伤害，并施加1层热邪。消耗。</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>生石膏甘辛大寒，清热泻火，除烦止渴。</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>equipment_ziwuliuzhu</t>
+          <t>yiyi</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>子午流注</t>
+          <t>薏苡除湿</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>装备牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="n">
-        <v>0</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>装备牌：非首回合的玩家回合开始额外抽1张牌。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_equipment/ziwuliuzhu.webp</t>
+          <t>block_cleanse_self</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>按时取穴，借时令流转调节气血。</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>equipment_ziwuliuzhu</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
       <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>获得4点格挡，并移除自身的1个负面状态。</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>薏苡仁甘淡凉，利水渗湿，健脾止泻。</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>chongrenbugu</t>
+          <t>yupingfeng</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>冲任不固</t>
+          <t>竹叶</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>敌方机制牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -6293,51 +7042,63 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F101" s="2" t="n">
-        <v>0</v>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>(敌方技能)使玩家失去所有正面状态。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/85.png</t>
+          <t>block</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>冲任气血亏虚，固摄无权。</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>获得20点格挡。消耗。</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>竹叶甘辛淡寒，清热除烦，生津利尿。</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>fenghanshubiao</t>
+          <t>yuzhu</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>风寒束表</t>
+          <t>玉竹生津</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>敌方机制牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -6350,108 +7111,116 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F102" s="2" t="n">
-        <v>0</v>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>(敌方技能)对玩家施加寒邪与虚弱。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/78.png</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>风寒之邪侵袭肌表。</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>yin_power_energy</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>(能力)回合开始时若有滋阴，获得1点真气。</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>玉竹甘微寒，养阴润燥，生津止渴。</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>ganhuowang</t>
+          <t>zexie</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>肝火旺</t>
+          <t>泽泻利水</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>敌方机制牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F103" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>(敌方能力)每回合开始，自身攻击力+2。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/76.png</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>肝气郁结，日久化火。</t>
-        </is>
-      </c>
-      <c r="J103" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K103" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>cleanse_damp_convert_block</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>移除自身所有湿邪，每层获得2点格挡。</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>泽泻甘淡寒，利水渗湿，泄热。</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>pixushikun</t>
+          <t>zhenwu</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>脾虚湿困</t>
+          <t>苍术</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>敌方机制牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6464,165 +7233,185 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F104" s="2" t="n">
-        <v>0</v>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>(敌方能力)玩家卡牌消耗增加1点。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/77.png</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>脾气虚弱，运化失职。</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>double_block_buff</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>本场战斗中，你的格挡效果翻倍。消耗。</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>苍术辛苦温，燥湿健脾，祛风散寒，明目。</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>qizhixueyu</t>
+          <t>zhimu</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>气滞血瘀</t>
+          <t>知母清热</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>敌方机制牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>(敌方能力)玩家每打出一张牌受到1点伤害。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/81.png</t>
+          <t>yin_attack_virtual_heat</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>气机郁滞，血行不畅。</t>
-        </is>
-      </c>
-      <c r="J105" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K105" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>获得1层滋阴。本回合你的攻击卡额外施加1层虚热。</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>知母苦甘寒，清热泻火，滋阴润燥。</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>reruyingxue</t>
+          <t>zhishi</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>热入营血</t>
+          <t>枳实行气</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>敌方机制牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>技能</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>0</v>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>(敌方能力)回合结束时造成热邪层数的伤害。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/79.png</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>温热病邪深入营分血分。</t>
-        </is>
-      </c>
-      <c r="J106" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K106" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>draw_if_attack</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>抽1张牌。如果本回合已打出攻击牌，额外抽1张。</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>枳实苦辛酸微寒，破气消积。</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>shenbunaqi</t>
+          <t>zhusha</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>肾不纳气</t>
+          <t>朱砂安神</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>敌方机制牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6635,108 +7424,120 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F107" s="2" t="n">
-        <v>0</v>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>(敌方技能)偷取玩家1点真气上限。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/80.png</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>肾气虚衰，摄纳无权。</t>
-        </is>
-      </c>
-      <c r="J107" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>attack_stun_chance</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
+      <c r="J107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>(能力)攻击卡有25%几率使敌人眩晕。</t>
+        </is>
+      </c>
+      <c r="O107" s="2" t="inlineStr">
+        <is>
+          <t>朱砂甘微寒，清心镇惊，安神解毒。</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>tanmengxinqiao</t>
+          <t>zouguan</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>痰蒙心窍</t>
+          <t>拔罐：走罐</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>敌方机制牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>能力</t>
+          <t>攻击</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
         <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>0</v>
+          <t>罕见</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>(敌方技能)使玩家眩晕1回合。</t>
+          <t>全体</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/83.png</t>
+          <t>aoe_damage</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
         <is>
-          <t>痰浊上蒙，阻闭清窍。</t>
-        </is>
-      </c>
-      <c r="J108" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K108" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J108" s="2" t="inlineStr"/>
+      <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>对所有敌人造成5点伤害。</t>
+        </is>
+      </c>
+      <c r="O108" s="2" t="inlineStr">
+        <is>
+          <t>走罐可行气活血，祛风散寒。</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>xinshenbujiao</t>
+          <t>zusanli</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>心肾不交</t>
+          <t>针刺：足三里</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>敌方机制牌</t>
+          <t>药材</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6749,96 +7550,43 @@
           <t>稀有</t>
         </is>
       </c>
-      <c r="F109" s="2" t="n">
-        <v>0</v>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>(敌方技能)下回合无法获得格挡。</t>
+          <t>自身</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>/assets/cards_player/82.png</t>
+          <t>zusanli_effect</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
         <is>
-          <t>心火亢盛，肾水不足。</t>
-        </is>
-      </c>
-      <c r="J109" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K109" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J109" s="2" t="inlineStr"/>
+      <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
       <c r="M109" s="2" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>yangmingfushi</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>阳明腑实</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>敌方机制牌</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G110" s="2" t="inlineStr">
-        <is>
-          <t>(敌方能力)回合结束时清除玩家所有护盾。</t>
-        </is>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>/assets/cards_player/84.png</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>邪热与腑实互结。</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>status_enemy</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>(能力)每当你打出攻击卡时，每层恢复1点生命。</t>
+        </is>
+      </c>
+      <c r="O109" s="2" t="inlineStr">
+        <is>
+          <t>足三里为“强壮要穴”，健脾和胃。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M111"/>
+  <autoFilter ref="A1:O109"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6849,211 +7597,56 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>类型</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>分类统计</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>药材牌</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n">
-        <v>76</v>
-      </c>
-    </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>药方牌</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>装备</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>药方</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
         <v>12</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>装备牌</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n">
-        <v>11</v>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>敌方机制牌</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>总计</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n"/>
-      <c r="B7" s="2" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>战斗类型</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>攻击</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>技能</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>能力</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="inlineStr">
-        <is>
-          <t>稀有度</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>非凡</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>稀有</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="n"/>
-      <c r="B17" s="2" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>药方蓝图</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>蓝图素材卡牌模板数</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>体质数量</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>每个体质起始牌组</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15 张</t>
-        </is>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>药材</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/卡牌清单.xlsx
+++ b/卡牌清单.xlsx
@@ -703,7 +703,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>干姜</t>
+          <t>干姜温中</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>半夏</t>
+          <t>半夏燥湿</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>苦桔梗</t>
+          <t>桔梗宣肺</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>熟地黄</t>
+          <t>熟地滋阴</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>薄荷</t>
+          <t>薄荷疏风</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>莪术</t>
+          <t>莪术破积</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1869,7 +1869,7 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>三棱</t>
+          <t>三棱破血</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>淡豆豉</t>
+          <t>豆豉宣郁</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>牛蒡子</t>
+          <t>牛蒡解毒</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>苏叶</t>
+          <t>苏叶解表</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>柴胡</t>
+          <t>柴胡疏肝</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>五味子</t>
+          <t>五味敛阴</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>人参</t>
+          <t>人参补气</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>细辛</t>
+          <t>细辛通窍</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>杏仁</t>
+          <t>杏仁降气</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>蒲公英</t>
+          <t>蒲公英消肿</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>天门冬</t>
+          <t>天冬养阴</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>荆芥穗</t>
+          <t>芥穗散风</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>葛根</t>
+          <t>葛根解肌</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>赤芍</t>
+          <t>赤芍凉血</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>厚朴</t>
+          <t>厚朴行气</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>生石膏</t>
+          <t>石膏清热</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -7024,7 +7024,7 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>竹叶</t>
+          <t>竹叶清心</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -7215,7 +7215,7 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>苍术</t>
+          <t>苍术健脾</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">

--- a/卡牌清单.xlsx
+++ b/卡牌清单.xlsx
@@ -7597,7 +7597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7622,17 +7622,17 @@
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>装备</t>
+          <t>药材牌</t>
         </is>
       </c>
       <c r="B3" s="5" t="n">
-        <v>11</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>药方</t>
+          <t>药方牌</t>
         </is>
       </c>
       <c r="B4" s="5" t="n">
@@ -7642,11 +7642,69 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>装备牌</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>85</v>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>敌方机制牌</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1主线(3幕) + 11支线</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>事件队列</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>线性(Act1→Act2→Act3→支线)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>地图密度</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>85%事件/10%商店/5%战斗</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>管理员密码</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>260208</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/卡牌清单.xlsx
+++ b/卡牌清单.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -45,6 +45,9 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
+      <b val="1"/>
+    </font>
+    <font>
       <b val="1"/>
     </font>
   </fonts>
@@ -88,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -99,6 +102,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1423,7 +1438,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2748,7 +2763,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -3832,7 +3847,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -5091,7 +5106,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -5282,7 +5297,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -5343,7 +5358,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -5794,7 +5809,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -6326,7 +6341,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -6647,7 +6662,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -6834,7 +6849,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>药材</t>
+          <t>敌方机制</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -7597,113 +7612,186 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="72" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>分类统计</t>
         </is>
       </c>
+      <c r="B1" s="6" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>分类</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>数量</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>药材牌</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
-        <v>85</v>
+      <c r="B3" s="8" t="n">
+        <v>75</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>药方牌</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
+      <c r="B4" s="8" t="n">
         <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>装备牌</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
+      <c r="B5" s="8" t="n">
         <v>11</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>敌方机制牌</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" s="9" t="n">
         <v>10</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="9" t="n"/>
+      <c r="B7" s="9" t="n"/>
+    </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>事件</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>1主线(3幕) + 11支线</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>事件队列</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>线性(Act1→Act2→Act3→支线)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>地图密度</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>85%事件/10%商店/5%战斗</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>管理员密码</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>260208</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="B12" s="9" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>药房合成</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>显示牌组/手牌/材料数量；每张候选牌显示同模板拥有数量xN（含x1）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>三兄弟Act1二哥</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>生命上限+2，金币+50（替代满血开局回血）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>资源加载</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>主页加载进度总量只统计critical/static预加载资源，不计入未预载GIF</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14：6个测试文件 / 71个测试通过；npm run build通过</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>更新日期</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>

--- a/卡牌清单.xlsx
+++ b/卡牌清单.xlsx
@@ -7646,7 +7646,7 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -7670,130 +7670,124 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>敌方机制牌</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="A6" s="9" t="n"/>
+      <c r="B6" s="9" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="n"/>
-      <c r="B7" s="9" t="n"/>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>事件</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>1主线(3幕) + 11支线</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>事件</t>
+          <t>事件队列</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>1主线(3幕) + 11支线</t>
+          <t>线性(Act1→Act2→Act3→支线)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>事件队列</t>
+          <t>地图密度</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>线性(Act1→Act2→Act3→支线)</t>
+          <t>85%事件/10%商店/5%战斗</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>地图密度</t>
+          <t>管理员密码</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>85%事件/10%商店/5%战斗</t>
+          <t>260208</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>管理员密码</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>260208</t>
-        </is>
-      </c>
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>药房合成</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>显示牌组/手牌/材料数量；每张候选牌显示同模板拥有数量xN（含x1）</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>药房合成</t>
+          <t>三兄弟Act1二哥</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>显示牌组/手牌/材料数量；每张候选牌显示同模板拥有数量xN（含x1）</t>
+          <t>生命上限+2，金币+50（替代满血开局回血）</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>三兄弟Act1二哥</t>
+          <t>资源加载</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>生命上限+2，金币+50（替代满血开局回血）</t>
+          <t>主页加载进度总量只统计critical/static预加载资源，不计入未预载GIF</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="9" t="inlineStr">
         <is>
-          <t>资源加载</t>
+          <t>测试</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>主页加载进度总量只统计critical/static预加载资源，不计入未预载GIF</t>
+          <t>2026-05-14：6个测试文件 / 71个测试通过；npm run build通过</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="9" t="inlineStr">
         <is>
-          <t>测试</t>
+          <t>更新日期</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>2026-05-14：6个测试文件 / 71个测试通过；npm run build通过</t>
+          <t>2026-05-14</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>更新日期</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
